--- a/artfynd/A 51085-2024 artfynd.xlsx
+++ b/artfynd/A 51085-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1038,130 +1038,6 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>92401707</v>
-      </c>
-      <c r="B5" t="n">
-        <v>58129</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>100117</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Långbensgroda</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Rana dalmatina</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Bonaparte, 1840</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>äggklumpar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>ägg</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Grettlinge, Fågelmara, Bl</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>556499</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6233586</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Blekinge</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Karlskrona</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Blekinge</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Jämjö</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2021-04-08</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2021-04-08</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Erik Fridolf</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Erik Fridolf</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51085-2024 artfynd.xlsx
+++ b/artfynd/A 51085-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89038450</v>
+        <v>92401707</v>
       </c>
       <c r="B2" t="n">
-        <v>57576</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58816</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -708,20 +703,41 @@
           <t>Bonaparte, 1840</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>äggklumpar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grettlinge 1:29, Bl</t>
+          <t>Grettlinge, Fågelmara, Bl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556496.7437231379</v>
+        <v>556499</v>
       </c>
       <c r="R2" t="n">
-        <v>6233585.759254507</v>
+        <v>6233586</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +761,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-03-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-03-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Utbredningskontroll långbensgroda.</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,269 +775,22 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marcus Törnberg</t>
+          <t>Erik Fridolf</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marcus Törnberg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av groddjur</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>93074652</v>
-      </c>
-      <c r="B3" t="n">
-        <v>57575</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>208250</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Åkergroda</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Rana arvalis</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>eDNA</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Grettlinge, Fågelmara, Bl</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>556498.9631769769</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6233586.344259587</v>
-      </c>
-      <c r="S3" t="n">
-        <v>5</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Blekinge</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Karlskrona</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Blekinge</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Jämjö</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2021-04-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2021-04-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
           <t>Erik Fridolf</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Erik Fridolf</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>93074651</v>
-      </c>
-      <c r="B4" t="n">
-        <v>57576</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>100117</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Långbensgroda</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Rana dalmatina</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Bonaparte, 1840</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>eDNA</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Grettlinge, Fågelmara, Bl</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>556498.9631769769</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6233586.344259587</v>
-      </c>
-      <c r="S4" t="n">
-        <v>5</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Blekinge</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Karlskrona</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Blekinge</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Jämjö</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2021-04-08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2021-04-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Erik Fridolf</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Erik Fridolf</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51085-2024 artfynd.xlsx
+++ b/artfynd/A 51085-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,8 +796,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92401707</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>